--- a/results/link-prediction-gcn/Link/5shot/PubMed/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/PubMed/GCN_total_results.xlsx
@@ -903,12 +903,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.4108±0.0000</t>
+          <t>0.4485±0.0328</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.4207±0.0000</t>
+          <t>0.4813±0.0263</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6045±0.0000</t>
+          <t>0.5275±0.0151</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.6045±0.0000</t>
+          <t>0.5275±0.0151</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6045±0.0000</t>
+          <t>0.5275±0.0151</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5302±0.0000</t>
+          <t>0.5926±0.0319</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6380±0.0000</t>
+          <t>0.6033±0.0520</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -963,387 +963,387 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>0.5723±0.1022</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4903±0.0153</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.4980±0.0124</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.4983±0.0012</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4988±0.0015</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6327±0.0950</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5367±0.0406</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5367±0.0406</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5367±0.0406</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6401±0.1000</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.7247±0.0141</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5481±0.0533</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4688±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4658±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4961±0.0028</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4942±0.0072</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.5001±0.0001</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0687</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.7043±0.0079</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.7043±0.0079</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.7043±0.0079</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5472±0.0667</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6846±0.0392</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.6791±0.0279</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.5370±0.0523</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5648±0.0095</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4842±0.0062</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5031±0.0148</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5018±0.0026</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6358±0.0146</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6899±0.0326</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6899±0.0326</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6899±0.0326</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6480±0.0450</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6924±0.0032</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6904±0.0281</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5051±0.0060</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5000±0.0001</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4480±0.0383</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4998±0.0002</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.7144±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.5686±0.0000</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5574±0.0801</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.6705±0.0136</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6705±0.0136</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.6705±0.0136</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5006±0.0008</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7132±0.0145</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.6650±0.0190</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.5548±0.0907</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4298±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4644±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4996±0.0006</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.4887±0.0158</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.6929±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.6929±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.6929±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.6431±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.6998±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5002±0.0002</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5002±0.0002</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5002±0.0002</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.6569±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4790±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4477±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.6722±0.0125</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5002±0.0003</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5033±0.0046</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4583±0.0210</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5010±0.0076</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.6812±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.7039±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.7039±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.7039±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.6763±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.7125±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7033±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4313±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4957±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.6727±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.6727±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.6727±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.6876±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7270±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.6828±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4851±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5113±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4875±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4556±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5109±0.0000</t>
+          <t>0.5173±0.0031</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5152±0.0061</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5152±0.0061</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5152±0.0061</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5147±0.0079</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5391±0.0000</t>
+          <t>0.5952±0.0426</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5378±0.0000</t>
+          <t>0.5188±0.0165</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.5768±0.0000</t>
+          <t>0.6074±0.0385</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.5597±0.0000</t>
+          <t>0.6462±0.0288</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7130±0.0000</t>
+          <t>0.6784±0.0076</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7130±0.0000</t>
+          <t>0.6784±0.0076</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7130±0.0000</t>
+          <t>0.6784±0.0076</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6725±0.0000</t>
+          <t>0.6723±0.0067</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7290±0.0000</t>
+          <t>0.7058±0.0181</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,387 +1425,387 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>0.7003±0.0476</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6354±0.0124</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6504±0.0104</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6634±0.0032</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6652±0.0018</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7272±0.0440</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6837±0.0192</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6837±0.0192</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6837±0.0192</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7314±0.0475</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7765±0.0117</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6895±0.0257</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.4444±0.3143</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6331±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6292±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6613±0.0047</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6582±0.0087</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.6666±0.0000</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6885±0.0309</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7643±0.0034</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7643±0.0034</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7643±0.0034</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6876±0.0295</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7499±0.0192</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7508±0.0155</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.5936±0.1034</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6963±0.0042</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6484±0.0076</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6482±0.0064</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6675±0.0011</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7310±0.0072</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7554±0.0163</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7554±0.0163</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7554±0.0163</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7368±0.0223</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7535±0.0032</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7563±0.0143</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.3961±0.2816</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6073±0.0407</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6665±0.0002</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6925±0.0361</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7487±0.0059</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7487±0.0059</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7487±0.0059</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6669±0.0004</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7714±0.0067</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7460±0.0099</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.6531±0.0096</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6661±0.0008</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6553±0.0159</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7736±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.2965±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.5744±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6234±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6669±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7616±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7616±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7616±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.7279±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.7650±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.7380±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6419±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.5958±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.7403±0.0083</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6668±0.0001</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6680±0.0019</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6157±0.0205</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6315±0.0178</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7495±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7627±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7627±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7627±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7469±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7653±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7629±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.5759±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6622±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7504±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7504±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7504±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.7559±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7810±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7551±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6354±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6660±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6708±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6510±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6056±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6709±0.0000</t>
+          <t>0.6735±0.0012</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6703±0.0019</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6703±0.0019</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6703±0.0019</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6755±0.0000</t>
+          <t>0.6726±0.0032</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6822±0.0000</t>
+          <t>0.6988±0.0096</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6811±0.0000</t>
+          <t>0.6736±0.0055</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8191±0.0000</t>
+          <t>0.7764±0.0651</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8811±0.0000</t>
+          <t>0.8862±0.0038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5426±0.0000</t>
+          <t>0.6851±0.0102</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5734±0.0000</t>
+          <t>0.6928±0.0069</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.8914±0.0000</t>
+          <t>0.8921±0.0017</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.8960±0.0000</t>
+          <t>0.8954±0.0027</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.8471±0.0000</t>
+          <t>0.8701±0.0256</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8470±0.0000</t>
+          <t>0.8834±0.0219</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8470±0.0000</t>
+          <t>0.8834±0.0219</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8470±0.0000</t>
+          <t>0.8834±0.0219</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8253±0.0000</t>
+          <t>0.8788±0.0126</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6707±0.0000</t>
+          <t>0.7234±0.0111</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7901±0.0000</t>
+          <t>0.7864±0.0277</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5687±0.0000</t>
+          <t>0.5891±0.0453</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8252±0.0000</t>
+          <t>0.8843±0.0440</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5460±0.0000</t>
+          <t>0.6973±0.0081</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6507±0.0000</t>
+          <t>0.7280±0.0349</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8496±0.0192</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8586±0.0174</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7588±0.0000</t>
+          <t>0.8799±0.0494</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6593±0.0000</t>
+          <t>0.9218±0.0102</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6593±0.0000</t>
+          <t>0.9218±0.0102</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6593±0.0000</t>
+          <t>0.9218±0.0102</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8697±0.0000</t>
+          <t>0.8757±0.0265</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8648±0.0000</t>
+          <t>0.8547±0.0224</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7703±0.0000</t>
+          <t>0.9241±0.0016</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5703±0.0000</t>
+          <t>0.6717±0.0563</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.8852±0.0000</t>
+          <t>0.8839±0.0027</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6134±0.0000</t>
+          <t>0.7209±0.0127</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7006±0.0000</t>
+          <t>0.7363±0.0084</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.8926±0.0000</t>
+          <t>0.8905±0.0029</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.9048±0.0000</t>
+          <t>0.8931±0.0069</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.8813±0.0000</t>
+          <t>0.8548±0.0028</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.9065±0.0000</t>
+          <t>0.8816±0.0078</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.9065±0.0000</t>
+          <t>0.8816±0.0078</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.9065±0.0000</t>
+          <t>0.8816±0.0078</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8710±0.0000</t>
+          <t>0.8493±0.0010</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8194±0.0000</t>
+          <t>0.8405±0.0102</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.8687±0.0000</t>
+          <t>0.8470±0.0177</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6378±0.0000</t>
+          <t>0.5538±0.0576</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.8701±0.0000</t>
+          <t>0.9044±0.0183</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4712±0.0000</t>
+          <t>0.7065±0.0085</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5864±0.0000</t>
+          <t>0.7080±0.0215</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.8881±0.0000</t>
+          <t>0.8912±0.0013</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.9006±0.0000</t>
+          <t>0.8929±0.0110</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8705±0.0000</t>
+          <t>0.9126±0.0116</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8741±0.0000</t>
+          <t>0.8814±0.0044</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8741±0.0000</t>
+          <t>0.8814±0.0044</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8741±0.0000</t>
+          <t>0.8814±0.0044</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8702±0.0000</t>
+          <t>0.9017±0.0187</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8478±0.0000</t>
+          <t>0.8386±0.0101</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8446±0.0000</t>
+          <t>0.8513±0.0087</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.5519±0.0000</t>
+          <t>0.5863±0.0753</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.8752±0.0000</t>
+          <t>0.8844±0.0055</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5338±0.0000</t>
+          <t>0.6787±0.0150</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6987±0.0000</t>
+          <t>0.7270±0.0119</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.8936±0.0000</t>
+          <t>0.8914±0.0043</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.9181±0.0000</t>
+          <t>0.8995±0.0102</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.8587±0.0000</t>
+          <t>0.8948±0.0209</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.9014±0.0000</t>
+          <t>0.8926±0.0092</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.9014±0.0000</t>
+          <t>0.8926±0.0092</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.9014±0.0000</t>
+          <t>0.8926±0.0092</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8717±0.0000</t>
+          <t>0.8946±0.0173</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8746±0.0000</t>
+          <t>0.8713±0.0087</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8549±0.0078</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.8191±0.0000</t>
+          <t>0.7737±0.0373</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.8974±0.0000</t>
+          <t>0.8915±0.0015</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5896±0.0000</t>
+          <t>0.6920±0.0145</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.7118±0.0000</t>
+          <t>0.7146±0.0177</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.8906±0.0000</t>
+          <t>0.8878±0.0011</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.8960±0.0000</t>
+          <t>0.8923±0.0020</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.8955±0.0000</t>
+          <t>0.8901±0.0038</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.8997±0.0000</t>
+          <t>0.8923±0.0057</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.8997±0.0000</t>
+          <t>0.8923±0.0057</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.8997±0.0000</t>
+          <t>0.8923±0.0057</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.9012±0.0000</t>
+          <t>0.8874±0.0025</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.7929±0.0000</t>
+          <t>0.8511±0.0109</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.8652±0.0000</t>
+          <t>0.8553±0.0183</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6545±0.0000</t>
+          <t>0.7661±0.0259</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.9049±0.0000</t>
+          <t>0.8850±0.0051</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4874±0.0000</t>
+          <t>0.5638±0.0608</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4934±0.0000</t>
+          <t>0.5874±0.0695</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.8902±0.0000</t>
+          <t>0.8802±0.0039</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.8227±0.0000</t>
+          <t>0.8470±0.0123</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.8820±0.0000</t>
+          <t>0.8681±0.0021</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7571±0.0000</t>
+          <t>0.7922±0.0530</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7571±0.0000</t>
+          <t>0.7922±0.0530</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7571±0.0000</t>
+          <t>0.7922±0.0530</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.8690±0.0000</t>
+          <t>0.8597±0.0024</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7547±0.0000</t>
+          <t>0.7462±0.0037</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7118±0.0000</t>
+          <t>0.8031±0.0638</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7664±0.0000</t>
+          <t>0.7463±0.0440</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8670±0.0000</t>
+          <t>0.8667±0.0016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5431±0.0000</t>
+          <t>0.7402±0.0264</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5867±0.0000</t>
+          <t>0.7412±0.0115</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8748±0.0000</t>
+          <t>0.8790±0.0038</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.8839±0.0000</t>
+          <t>0.8834±0.0026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8442±0.0000</t>
+          <t>0.8615±0.0163</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.8394±0.0000</t>
+          <t>0.8782±0.0165</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8394±0.0000</t>
+          <t>0.8782±0.0165</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8394±0.0000</t>
+          <t>0.8782±0.0165</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8311±0.0000</t>
+          <t>0.8668±0.0099</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6949±0.0000</t>
+          <t>0.7518±0.0132</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7808±0.0000</t>
+          <t>0.7791±0.0281</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6490±0.0000</t>
+          <t>0.6673±0.0232</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8447±0.0000</t>
+          <t>0.8862±0.0379</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5432±0.0000</t>
+          <t>0.7187±0.0187</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7064±0.0000</t>
+          <t>0.7466±0.0395</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8462±0.0060</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8508±0.0040</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8022±0.0000</t>
+          <t>0.8804±0.0443</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.9132±0.0081</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.9133±0.0081</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.9132±0.0081</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8798±0.0000</t>
+          <t>0.8827±0.0218</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8310±0.0000</t>
+          <t>0.8203±0.0240</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7862±0.0000</t>
+          <t>0.9111±0.0033</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6476±0.0000</t>
+          <t>0.6970±0.0270</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8682±0.0000</t>
+          <t>0.8632±0.0030</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6209±0.0000</t>
+          <t>0.7703±0.0223</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7772±0.0000</t>
+          <t>0.7795±0.0100</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.8762±0.0000</t>
+          <t>0.8772±0.0037</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8982±0.0000</t>
+          <t>0.8733±0.0131</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8775±0.0000</t>
+          <t>0.8562±0.0086</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.9090±0.0000</t>
+          <t>0.8886±0.0074</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.9090±0.0000</t>
+          <t>0.8886±0.0074</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.9090±0.0000</t>
+          <t>0.8886±0.0074</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8695±0.0000</t>
+          <t>0.8520±0.0069</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8103±0.0000</t>
+          <t>0.8309±0.0119</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.8655±0.0000</t>
+          <t>0.8465±0.0196</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6848±0.0000</t>
+          <t>0.6348±0.0265</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8781±0.0000</t>
+          <t>0.9016±0.0172</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4852±0.0000</t>
+          <t>0.7282±0.0132</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5791±0.0000</t>
+          <t>0.7127±0.0211</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.8620±0.0000</t>
+          <t>0.8790±0.0008</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.8901±0.0000</t>
+          <t>0.8870±0.0168</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8806±0.0000</t>
+          <t>0.9124±0.0112</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8827±0.0000</t>
+          <t>0.8903±0.0019</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8827±0.0000</t>
+          <t>0.8903±0.0019</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8827±0.0000</t>
+          <t>0.8903±0.0019</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8809±0.0000</t>
+          <t>0.9046±0.0158</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8365±0.0000</t>
+          <t>0.8233±0.0099</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8431±0.0000</t>
+          <t>0.8511±0.0104</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6269±0.0000</t>
+          <t>0.6553±0.0499</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.8635±0.0000</t>
+          <t>0.8680±0.0071</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5391±0.0000</t>
+          <t>0.7478±0.0034</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7460±0.0000</t>
+          <t>0.7625±0.0054</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.8772±0.0000</t>
+          <t>0.8757±0.0039</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.9004±0.0000</t>
+          <t>0.8879±0.0106</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.8541±0.0000</t>
+          <t>0.8889±0.0223</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.9026±0.0000</t>
+          <t>0.8945±0.0062</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.9026±0.0000</t>
+          <t>0.8945±0.0062</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.9026±0.0000</t>
+          <t>0.8945±0.0062</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8742±0.0000</t>
+          <t>0.8843±0.0159</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8415±0.0000</t>
+          <t>0.8481±0.0083</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8548±0.0000</t>
+          <t>0.8560±0.0031</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7941±0.0000</t>
+          <t>0.7495±0.0209</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.8730±0.0000</t>
+          <t>0.8634±0.0016</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6167±0.0000</t>
+          <t>0.7354±0.0101</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7693±0.0000</t>
+          <t>0.7844±0.0123</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.8738±0.0000</t>
+          <t>0.8728±0.0017</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8769±0.0000</t>
+          <t>0.8721±0.0005</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8751±0.0000</t>
+          <t>0.8673±0.0034</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.8783±0.0000</t>
+          <t>0.8740±0.0095</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.8783±0.0000</t>
+          <t>0.8740±0.0095</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.8783±0.0000</t>
+          <t>0.8740±0.0095</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8777±0.0000</t>
+          <t>0.8653±0.0025</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.8140±0.0000</t>
+          <t>0.8651±0.0081</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.8462±0.0000</t>
+          <t>0.8428±0.0228</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6763±0.0000</t>
+          <t>0.7470±0.0178</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.8871±0.0000</t>
+          <t>0.8695±0.0046</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4938±0.0000</t>
+          <t>0.5647±0.0536</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5021±0.0000</t>
+          <t>0.5809±0.0621</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.8684±0.0000</t>
+          <t>0.8668±0.0022</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.8421±0.0000</t>
+          <t>0.8545±0.0068</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8685±0.0000</t>
+          <t>0.8574±0.0059</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6952±0.0000</t>
+          <t>0.7723±0.0632</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6952±0.0000</t>
+          <t>0.7723±0.0632</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6952±0.0000</t>
+          <t>0.7723±0.0632</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.8592±0.0000</t>
+          <t>0.8511±0.0044</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7296±0.0000</t>
+          <t>0.7226±0.0026</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6566±0.0000</t>
+          <t>0.7777±0.0646</t>
         </is>
       </c>
     </row>
